--- a/tame_output/ON/bt/strategyON_20231023.xlsx
+++ b/tame_output/ON/bt/strategyON_20231023.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>69.5%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.6%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.0%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1758"/>
+  <dimension ref="A1:G1759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41944,7 +41944,7 @@
         <v>45220</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.911674046606653</v>
+        <v>2.91290325494784</v>
       </c>
       <c r="C1758" t="n">
         <v>2.965146865274802</v>
@@ -41960,6 +41960,29 @@
       </c>
       <c r="G1758" t="n">
         <v>4.26372745976593</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="2" t="n">
+        <v>45221</v>
+      </c>
+      <c r="B1759" t="n">
+        <v>2.930344769383407</v>
+      </c>
+      <c r="C1759" t="n">
+        <v>2.964689051375926</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>1.566859663870223</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>3.591076492610268</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>2.157302608503688</v>
+      </c>
+      <c r="G1759" t="n">
+        <v>4.259070616478141</v>
       </c>
     </row>
   </sheetData>
